--- a/MGA Wednesday Night 2026.xlsx
+++ b/MGA Wednesday Night 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jburns\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ECA88FF-DCCE-442E-9647-2F6E8AD29838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B59049EE-FDFF-4F92-ACCF-F9F4BE861797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17175" yWindow="-15870" windowWidth="25440" windowHeight="15270" xr2:uid="{8351B9A9-2A04-4410-9EAE-0FAE34D4202D}"/>
+    <workbookView xWindow="-11625" yWindow="-18120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{8351B9A9-2A04-4410-9EAE-0FAE34D4202D}"/>
   </bookViews>
   <sheets>
     <sheet name="MGA Wed Totals " sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="162">
   <si>
     <t>Golfer1</t>
   </si>
@@ -617,7 +617,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -651,6 +651,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -855,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -941,11 +947,40 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1272,9 +1307,6 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1292,19 +1324,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -1316,18 +1335,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1949,7 +1956,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -2048,10 +2055,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.5</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -2135,7 +2142,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>1.5</c:v>
@@ -2180,7 +2187,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>0</c:v>
@@ -3252,7 +3259,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -3351,10 +3358,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.5</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
@@ -3669,7 +3676,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -3678,7 +3685,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -3702,7 +3709,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -3714,10 +3721,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>8</c:v>
@@ -3741,7 +3748,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>2</c:v>
@@ -3762,16 +3769,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>2</c:v>
@@ -3795,7 +3802,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="49">
                   <c:v>0</c:v>
@@ -4063,7 +4070,7 @@
                         <c:v>-1</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>2.875</c:v>
+                        <c:v>2.6666666666666665</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -4072,7 +4079,7 @@
                         <c:v>5.5</c:v>
                       </c:pt>
                       <c:pt idx="9">
-                        <c:v>0</c:v>
+                        <c:v>-0.33333333333333331</c:v>
                       </c:pt>
                       <c:pt idx="10">
                         <c:v>0</c:v>
@@ -4096,7 +4103,7 @@
                         <c:v>-1</c:v>
                       </c:pt>
                       <c:pt idx="17">
-                        <c:v>-0.33333333333333331</c:v>
+                        <c:v>0.14285714285714285</c:v>
                       </c:pt>
                       <c:pt idx="18">
                         <c:v>0</c:v>
@@ -4108,10 +4115,10 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="21">
-                        <c:v>3.3333333333333335</c:v>
+                        <c:v>2.75</c:v>
                       </c:pt>
                       <c:pt idx="22">
-                        <c:v>0.8</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="23">
                         <c:v>-0.5</c:v>
@@ -4135,7 +4142,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="30">
-                        <c:v>-0.66666666666666663</c:v>
+                        <c:v>-0.25</c:v>
                       </c:pt>
                       <c:pt idx="31">
                         <c:v>1</c:v>
@@ -4156,16 +4163,16 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="37">
-                        <c:v>-2.75</c:v>
+                        <c:v>-1.8</c:v>
                       </c:pt>
                       <c:pt idx="38">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="39">
-                        <c:v>1.6666666666666667</c:v>
+                        <c:v>1.6</c:v>
                       </c:pt>
                       <c:pt idx="40">
-                        <c:v>0.8571428571428571</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="41">
                         <c:v>1.5</c:v>
@@ -4189,7 +4196,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="48">
-                        <c:v>2.5</c:v>
+                        <c:v>2.3333333333333335</c:v>
                       </c:pt>
                       <c:pt idx="49">
                         <c:v>0</c:v>
@@ -4204,7 +4211,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="53">
-                        <c:v>3</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="54">
                         <c:v>0</c:v>
@@ -4240,7 +4247,7 @@
                         <c:v>1.3333333333333333</c:v>
                       </c:pt>
                       <c:pt idx="65">
-                        <c:v>2.125</c:v>
+                        <c:v>2.1111111111111112</c:v>
                       </c:pt>
                       <c:pt idx="66">
                         <c:v>3</c:v>
@@ -4249,13 +4256,13 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="68">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="69">
                         <c:v>3.3333333333333335</c:v>
                       </c:pt>
                       <c:pt idx="70">
-                        <c:v>0</c:v>
+                        <c:v>0.33333333333333331</c:v>
                       </c:pt>
                       <c:pt idx="71">
                         <c:v>-2</c:v>
@@ -4267,7 +4274,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="74">
-                        <c:v>4</c:v>
+                        <c:v>3.6</c:v>
                       </c:pt>
                       <c:pt idx="75">
                         <c:v>4</c:v>
@@ -4288,13 +4295,13 @@
                         <c:v>-1</c:v>
                       </c:pt>
                       <c:pt idx="81">
-                        <c:v>3</c:v>
+                        <c:v>3.125</c:v>
                       </c:pt>
                       <c:pt idx="82">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="83">
-                        <c:v>1</c:v>
+                        <c:v>-0.66666666666666663</c:v>
                       </c:pt>
                       <c:pt idx="84">
                         <c:v>0</c:v>
@@ -5736,8 +5743,8 @@
   <tableColumns count="39">
     <tableColumn id="1" xr3:uid="{5656029D-01CC-4E6C-909B-9A472F1F027A}" name="Golfer" totalsRowLabel="guest 1" dataDxfId="26"/>
     <tableColumn id="57" xr3:uid="{57087183-1C70-4674-86C7-E66CB9FA236B}" name="2 Pot" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{33712F80-A8F3-4B0D-9232-7362D9DD6B58}" name="Wins " dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="20" xr3:uid="{8C7CB8C2-BBD7-433D-BA98-AE62F92030AF}" name="Avg Score" dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="2" xr3:uid="{33712F80-A8F3-4B0D-9232-7362D9DD6B58}" name="Wins " dataDxfId="24" totalsRowDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{8C7CB8C2-BBD7-433D-BA98-AE62F92030AF}" name="Avg Score" dataDxfId="23" totalsRowDxfId="1">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{E6575482-81EE-478B-920F-E7799D374431}" name="11-Mar"/>
@@ -5747,7 +5754,7 @@
     <tableColumn id="5" xr3:uid="{715481D5-DC72-4A46-ABE1-FC4D2D7BA8F5}" name="25-Mar" totalsRowFunction="custom">
       <totalsRowFormula array="1">IFERROR(INDEX(CHOOSE(MATCH($X95,INDEX($B:$R,MATCH(AD$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AD$1,$A:$A,0)),INDEX($F:$F,MATCH(AD$1,$A:$A,0)),INDEX($I:$I,MATCH(AD$1,$A:$A,0)),INDEX($L:$L,MATCH(AD$1,$A:$A,0)),INDEX($O:$O,MATCH(AD$1,$A:$A,0)),INDEX($R:$R,MATCH(AD$1,$A:$A,0))),1),"")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4A1D91F6-3223-40A6-9130-B7565B61D717}" name="01-Apr" totalsRowFunction="custom" dataDxfId="20">
+    <tableColumn id="6" xr3:uid="{4A1D91F6-3223-40A6-9130-B7565B61D717}" name="01-Apr" totalsRowFunction="custom" dataDxfId="22">
       <totalsRowFormula array="1">IFERROR(INDEX(CHOOSE(MATCH($X95,INDEX($B:$R,MATCH(AE$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AE$1,$A:$A,0)),INDEX($F:$F,MATCH(AE$1,$A:$A,0)),INDEX($I:$I,MATCH(AE$1,$A:$A,0)),INDEX($L:$L,MATCH(AE$1,$A:$A,0)),INDEX($O:$O,MATCH(AE$1,$A:$A,0)),INDEX($R:$R,MATCH(AE$1,$A:$A,0))),1),"")</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{C58B4902-6245-4AFA-86E5-3E4740FC71F7}" name="08-Apr" totalsRowFunction="custom">
@@ -5765,7 +5772,7 @@
     <tableColumn id="11" xr3:uid="{16FF3475-5159-4E26-883A-4677541D8DA3}" name="06-May" totalsRowFunction="custom">
       <totalsRowFormula array="1">IFERROR(INDEX(CHOOSE(MATCH($X95,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{82F28C2C-C59B-4FC7-9837-199F81D20A2E}" name="13-May" totalsRowFunction="custom" dataDxfId="19">
+    <tableColumn id="12" xr3:uid="{82F28C2C-C59B-4FC7-9837-199F81D20A2E}" name="13-May" totalsRowFunction="custom" dataDxfId="21">
       <totalsRowFormula array="1">IFERROR(INDEX(CHOOSE(MATCH($X95,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</totalsRowFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{670C3330-0356-4329-B517-C70E6ECE3FDE}" name="20-May" totalsRowFunction="custom">
@@ -5835,10 +5842,10 @@
       <totalsRowFormula array="1">IFERROR(INDEX(CHOOSE(MATCH($X95,INDEX($B:$R,MATCH(BG$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(BG$1,$A:$A,0)),INDEX($F:$F,MATCH(BG$1,$A:$A,0)),INDEX($I:$I,MATCH(BG$1,$A:$A,0)),INDEX($L:$L,MATCH(BG$1,$A:$A,0)),INDEX($O:$O,MATCH(BG$1,$A:$A,0)),INDEX($R:$R,MATCH(BG$1,$A:$A,0))),1),"")</totalsRowFormula>
     </tableColumn>
     <tableColumn id="54" xr3:uid="{1E835546-CC77-44FB-A206-C3D65527A522}" name="Column33"/>
-    <tableColumn id="19" xr3:uid="{65918298-DC7D-4E04-AC92-1F67A76149D9}" name="Average " dataDxfId="18" totalsRowDxfId="17">
+    <tableColumn id="19" xr3:uid="{65918298-DC7D-4E04-AC92-1F67A76149D9}" name="Average " dataDxfId="20" totalsRowDxfId="0">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[11-Mar]:[24-Jun]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{6294E62B-7923-4916-9A60-99EE39091F81}" name="number of rounds" dataDxfId="16">
+    <tableColumn id="21" xr3:uid="{6294E62B-7923-4916-9A60-99EE39091F81}" name="number of rounds" dataDxfId="19">
       <calculatedColumnFormula>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5847,26 +5854,26 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E4C70A5D-6B84-4387-AEAE-CB1DA8C0196D}" name="Table3" displayName="Table3" ref="A1:E91" totalsRowCount="1" headerRowDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E4C70A5D-6B84-4387-AEAE-CB1DA8C0196D}" name="Table3" displayName="Table3" ref="A1:E91" totalsRowCount="1" headerRowDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="A1:E90" xr:uid="{E4C70A5D-6B84-4387-AEAE-CB1DA8C0196D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E82">
     <sortCondition ref="E1:E82"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A95ACC15-4257-4B5B-809A-A342E98275C9}" name="Golfer" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="1" xr3:uid="{A95ACC15-4257-4B5B-809A-A342E98275C9}" name="Golfer" dataDxfId="16" totalsRowDxfId="15">
       <calculatedColumnFormula>Table2[[#This Row],[Golfer]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FF69BD9B-D43D-48AB-ADD7-A191C984280D}" name="Wins " dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="2" xr3:uid="{FF69BD9B-D43D-48AB-ADD7-A191C984280D}" name="Wins " dataDxfId="14" totalsRowDxfId="13">
       <calculatedColumnFormula>SUM(Table2[[#This Row],[Wins ]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AC1B48CA-8BE1-40DF-B771-21F32371C651}" name="Times @ Tee" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="4" xr3:uid="{AC1B48CA-8BE1-40DF-B771-21F32371C651}" name="Times @ Tee" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="11">
       <calculatedColumnFormula>SUM(Table2[[#This Row],[number of rounds]])</calculatedColumnFormula>
       <totalsRowFormula>SUM(C2:C90)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{46BAED46-B14D-4DC9-B20E-3965500DC78C}" name="2Pot" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="5" xr3:uid="{46BAED46-B14D-4DC9-B20E-3965500DC78C}" name="2Pot" dataDxfId="10" totalsRowDxfId="9">
       <calculatedColumnFormula>SUM(Table2[[#This Row],[2 Pot]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8EAAB6CC-373B-41C3-9E11-626B39F4890B}" name="Avg NET Score" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="3" xr3:uid="{8EAAB6CC-373B-41C3-9E11-626B39F4890B}" name="Avg NET Score" dataDxfId="8" totalsRowDxfId="7">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5875,16 +5882,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8FA25A3D-A47C-40D3-8121-96E0DF6BF6E7}" name="Table4" displayName="Table4" ref="A1:B83" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8FA25A3D-A47C-40D3-8121-96E0DF6BF6E7}" name="Table4" displayName="Table4" ref="A1:B83" totalsRowShown="0" headerRowDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="A1:B83" xr:uid="{8FA25A3D-A47C-40D3-8121-96E0DF6BF6E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:B63">
     <sortCondition descending="1" ref="B1:B83"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{470B2B7E-560D-4F3F-A6F3-C286DBA1A8D5}" name="Golfer" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{470B2B7E-560D-4F3F-A6F3-C286DBA1A8D5}" name="Golfer" dataDxfId="4">
       <calculatedColumnFormula>Table2[[#This Row],[Golfer]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{60F2A4D1-6EF3-42EF-995D-742E4BA5E86F}" name="2 Pot" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{60F2A4D1-6EF3-42EF-995D-742E4BA5E86F}" name="2 Pot" dataDxfId="3">
       <calculatedColumnFormula>SUM(Table2[[#This Row],[2 Pot]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6236,8 +6243,8 @@
     <col min="26" max="26" width="10.59765625" customWidth="1"/>
     <col min="27" max="27" width="10.59765625" style="4" customWidth="1"/>
     <col min="28" max="31" width="9.1328125" hidden="1" customWidth="1"/>
-    <col min="32" max="36" width="9" hidden="1" customWidth="1"/>
-    <col min="37" max="44" width="9" customWidth="1"/>
+    <col min="32" max="37" width="9" hidden="1" customWidth="1"/>
+    <col min="38" max="44" width="9" customWidth="1"/>
     <col min="45" max="57" width="9.06640625" customWidth="1"/>
     <col min="61" max="61" width="9.1328125" style="4"/>
     <col min="62" max="62" width="9" customWidth="1"/>
@@ -7357,11 +7364,11 @@
         <v>104</v>
       </c>
       <c r="Z8" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2.875</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AB8">
         <v>6</v>
@@ -7391,9 +7398,8 @@
       <c r="AJ8">
         <v>3</v>
       </c>
-      <c r="AK8" t="str" cm="1">
-        <f t="array" ref="AK8">IFERROR(INDEX(CHOOSE(MATCH($X8,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK8">
+        <v>1</v>
       </c>
       <c r="AL8" t="str" cm="1">
         <f t="array" ref="AL8">IFERROR(INDEX(CHOOSE(MATCH($X8,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -7485,11 +7491,11 @@
       </c>
       <c r="BI8" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2.875</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="BJ8">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.45">
@@ -7855,7 +7861,7 @@
       <c r="Z11" s="6"/>
       <c r="AA11" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0</v>
+        <v>-0.33333333333333331</v>
       </c>
       <c r="AC11" t="str" cm="1">
         <f t="array" ref="AC11">IFERROR(INDEX(CHOOSE(MATCH($X11,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -7887,9 +7893,8 @@
         <f t="array" ref="AJ11">IFERROR(INDEX(CHOOSE(MATCH($X11,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK11" t="str" cm="1">
-        <f t="array" ref="AK11">IFERROR(INDEX(CHOOSE(MATCH($X11,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK11">
+        <v>-1</v>
       </c>
       <c r="AL11" t="str" cm="1">
         <f t="array" ref="AL11">IFERROR(INDEX(CHOOSE(MATCH($X11,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -7981,11 +7986,11 @@
       </c>
       <c r="BI11" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0</v>
+        <v>-0.33333333333333331</v>
       </c>
       <c r="BJ11">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.45">
@@ -9209,7 +9214,7 @@
       </c>
       <c r="AA19" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>-0.33333333333333331</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="AB19">
         <v>-4</v>
@@ -9241,9 +9246,8 @@
         <f t="array" ref="AJ19">IFERROR(INDEX(CHOOSE(MATCH($X19,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK19" t="str" cm="1">
-        <f t="array" ref="AK19">IFERROR(INDEX(CHOOSE(MATCH($X19,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK19">
+        <v>3</v>
       </c>
       <c r="AL19" t="str" cm="1">
         <f t="array" ref="AL19">IFERROR(INDEX(CHOOSE(MATCH($X19,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -9335,11 +9339,11 @@
       </c>
       <c r="BI19" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>-0.33333333333333331</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="BJ19">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.45">
@@ -9880,7 +9884,7 @@
       <c r="Z23" s="6"/>
       <c r="AA23" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3.3333333333333335</v>
+        <v>2.75</v>
       </c>
       <c r="AC23" t="str" cm="1">
         <f t="array" ref="AC23">IFERROR(INDEX(CHOOSE(MATCH($X23,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -9911,9 +9915,8 @@
       <c r="AJ23">
         <v>2</v>
       </c>
-      <c r="AK23" t="str" cm="1">
-        <f t="array" ref="AK23">IFERROR(INDEX(CHOOSE(MATCH($X23,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK23">
+        <v>1</v>
       </c>
       <c r="AL23" t="str" cm="1">
         <f t="array" ref="AL23">IFERROR(INDEX(CHOOSE(MATCH($X23,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -10005,11 +10008,11 @@
       </c>
       <c r="BI23" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3.3333333333333335</v>
+        <v>2.75</v>
       </c>
       <c r="BJ23">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.45">
@@ -10049,7 +10052,7 @@
       </c>
       <c r="AA24" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB24">
         <v>0</v>
@@ -10082,9 +10085,8 @@
       <c r="AJ24">
         <v>5</v>
       </c>
-      <c r="AK24" t="str" cm="1">
-        <f t="array" ref="AK24">IFERROR(INDEX(CHOOSE(MATCH($X24,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK24">
+        <v>2</v>
       </c>
       <c r="AL24" t="str" cm="1">
         <f t="array" ref="AL24">IFERROR(INDEX(CHOOSE(MATCH($X24,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -10176,11 +10178,11 @@
       </c>
       <c r="BI24" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BJ24">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.45">
@@ -11444,7 +11446,7 @@
       </c>
       <c r="AA32" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>-0.66666666666666663</v>
+        <v>-0.25</v>
       </c>
       <c r="AC32" t="str" cm="1">
         <f t="array" ref="AC32">IFERROR(INDEX(CHOOSE(MATCH($X32,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -11475,9 +11477,8 @@
         <f t="array" ref="AJ32">IFERROR(INDEX(CHOOSE(MATCH($X32,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK32" t="str" cm="1">
-        <f t="array" ref="AK32">IFERROR(INDEX(CHOOSE(MATCH($X32,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK32">
+        <v>1</v>
       </c>
       <c r="AL32" t="str" cm="1">
         <f t="array" ref="AL32">IFERROR(INDEX(CHOOSE(MATCH($X32,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -11569,11 +11570,11 @@
       </c>
       <c r="BI32" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>-0.66666666666666663</v>
+        <v>-0.25</v>
       </c>
       <c r="BJ32">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.45">
@@ -12667,7 +12668,7 @@
       </c>
       <c r="AA39" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>-2.75</v>
+        <v>-1.8</v>
       </c>
       <c r="AB39">
         <v>-2</v>
@@ -12701,9 +12702,8 @@
         <f t="array" ref="AJ39">IFERROR(INDEX(CHOOSE(MATCH($X39,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK39" t="str" cm="1">
-        <f t="array" ref="AK39">IFERROR(INDEX(CHOOSE(MATCH($X39,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK39">
+        <v>2</v>
       </c>
       <c r="AL39" t="str" cm="1">
         <f t="array" ref="AL39">IFERROR(INDEX(CHOOSE(MATCH($X39,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -12795,11 +12795,11 @@
       </c>
       <c r="BI39" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>-2.75</v>
+        <v>-1.8</v>
       </c>
       <c r="BJ39">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.45">
@@ -13028,11 +13028,11 @@
         <v>28</v>
       </c>
       <c r="Z41" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA41" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>1.6666666666666667</v>
+        <v>1.6</v>
       </c>
       <c r="AB41">
         <v>1</v>
@@ -13061,9 +13061,8 @@
       <c r="AJ41">
         <v>0</v>
       </c>
-      <c r="AK41" t="str" cm="1">
-        <f t="array" ref="AK41">IFERROR(INDEX(CHOOSE(MATCH($X41,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK41">
+        <v>1</v>
       </c>
       <c r="AL41" t="str" cm="1">
         <f t="array" ref="AL41">IFERROR(INDEX(CHOOSE(MATCH($X41,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -13155,11 +13154,11 @@
       </c>
       <c r="BI41" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>1.6666666666666667</v>
+        <v>1.6</v>
       </c>
       <c r="BJ41">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.45">
@@ -13223,11 +13222,11 @@
         <v>1</v>
       </c>
       <c r="Z42" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA42" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="AB42">
         <v>0</v>
@@ -13258,9 +13257,8 @@
       <c r="AJ42">
         <v>3</v>
       </c>
-      <c r="AK42" t="str" cm="1">
-        <f t="array" ref="AK42">IFERROR(INDEX(CHOOSE(MATCH($X42,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK42">
+        <v>2</v>
       </c>
       <c r="AL42" t="str" cm="1">
         <f t="array" ref="AL42">IFERROR(INDEX(CHOOSE(MATCH($X42,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -13352,11 +13350,11 @@
       </c>
       <c r="BI42" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="BJ42">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.45">
@@ -14585,7 +14583,7 @@
       <c r="Z50" s="6"/>
       <c r="AA50" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2.5</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="AB50">
         <v>3</v>
@@ -14621,9 +14619,8 @@
         <f t="array" ref="AJ50">IFERROR(INDEX(CHOOSE(MATCH($X50,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK50" t="str" cm="1">
-        <f t="array" ref="AK50">IFERROR(INDEX(CHOOSE(MATCH($X50,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK50">
+        <v>2</v>
       </c>
       <c r="AL50" t="str" cm="1">
         <f t="array" ref="AL50">IFERROR(INDEX(CHOOSE(MATCH($X50,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -14715,11 +14712,11 @@
       </c>
       <c r="BI50" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2.5</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="BJ50">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:62" x14ac:dyDescent="0.45">
@@ -15456,7 +15453,7 @@
       <c r="Z55" s="6"/>
       <c r="AA55" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC55" t="str" cm="1">
         <f t="array" ref="AC55">IFERROR(INDEX(CHOOSE(MATCH($X55,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -15489,9 +15486,8 @@
       <c r="AJ55">
         <v>3</v>
       </c>
-      <c r="AK55" t="str" cm="1">
-        <f t="array" ref="AK55">IFERROR(INDEX(CHOOSE(MATCH($X55,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK55">
+        <v>5</v>
       </c>
       <c r="AL55" t="str" cm="1">
         <f t="array" ref="AL55">IFERROR(INDEX(CHOOSE(MATCH($X55,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -15583,11 +15579,11 @@
       </c>
       <c r="BI55" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ55">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:62" x14ac:dyDescent="0.45">
@@ -16282,10 +16278,36 @@
       </c>
     </row>
     <row r="60" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A60" s="1"/>
+      <c r="A60" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="E60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>29</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="K60" t="s">
+        <v>144</v>
+      </c>
+      <c r="L60">
+        <v>4</v>
+      </c>
       <c r="T60">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X60" t="s">
         <v>32</v>
@@ -16428,10 +16450,48 @@
       </c>
     </row>
     <row r="61" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A61" s="1"/>
+      <c r="A61" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="H61" t="s">
+        <v>85</v>
+      </c>
+      <c r="I61">
+        <v>5</v>
+      </c>
+      <c r="K61" t="s">
+        <v>48</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="N61" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="O61" s="45">
+        <v>7</v>
+      </c>
+      <c r="P61">
+        <v>1</v>
+      </c>
       <c r="T61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
       </c>
       <c r="X61" t="s">
         <v>147</v>
@@ -16578,10 +16638,36 @@
       </c>
     </row>
     <row r="62" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A62" s="1"/>
+      <c r="A62" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B62" t="s">
+        <v>58</v>
+      </c>
+      <c r="C62">
+        <v>-1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="H62" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>91</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
       <c r="T62">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X62" t="s">
         <v>94</v>
@@ -16725,11 +16811,48 @@
       </c>
     </row>
     <row r="63" spans="1:62" x14ac:dyDescent="0.45">
-      <c r="A63" s="1"/>
-      <c r="T63">
+      <c r="A63" s="44">
+        <v>46155</v>
+      </c>
+      <c r="B63" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="39">
+        <v>1</v>
+      </c>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="39">
+        <v>1</v>
+      </c>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I63" s="39">
+        <v>-4</v>
+      </c>
+      <c r="J63" s="39"/>
+      <c r="K63" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="L63" s="39">
+        <v>2</v>
+      </c>
+      <c r="M63" s="39"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="39"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="39"/>
+      <c r="T63" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="U63" s="39"/>
       <c r="X63" t="s">
         <v>107</v>
       </c>
@@ -17321,7 +17444,7 @@
       </c>
       <c r="AA67" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2.125</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="AB67">
         <v>-1</v>
@@ -17351,9 +17474,8 @@
       <c r="AJ67">
         <v>0</v>
       </c>
-      <c r="AK67" t="str" cm="1">
-        <f t="array" ref="AK67">IFERROR(INDEX(CHOOSE(MATCH($X67,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK67">
+        <v>2</v>
       </c>
       <c r="AL67" t="str" cm="1">
         <f t="array" ref="AL67">IFERROR(INDEX(CHOOSE(MATCH($X67,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -17445,11 +17567,11 @@
       </c>
       <c r="BI67" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2.125</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="BJ67">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:62" x14ac:dyDescent="0.45">
@@ -17754,10 +17876,13 @@
       <c r="X70" t="s">
         <v>38</v>
       </c>
+      <c r="Y70">
+        <v>1</v>
+      </c>
       <c r="Z70" s="6"/>
-      <c r="AA70" s="10" t="e">
+      <c r="AA70" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>#DIV/0!</v>
+        <v>7</v>
       </c>
       <c r="AC70" t="str" cm="1">
         <f t="array" ref="AC70">IFERROR(INDEX(CHOOSE(MATCH($X70,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -17791,9 +17916,8 @@
         <f t="array" ref="AJ70">IFERROR(INDEX(CHOOSE(MATCH($X70,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK70" t="str" cm="1">
-        <f t="array" ref="AK70">IFERROR(INDEX(CHOOSE(MATCH($X70,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK70">
+        <v>7</v>
       </c>
       <c r="AL70" t="str" cm="1">
         <f t="array" ref="AL70">IFERROR(INDEX(CHOOSE(MATCH($X70,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -17883,13 +18007,13 @@
         <f t="array" ref="BG70">IFERROR(INDEX(CHOOSE(MATCH($X70,INDEX($B:$R,MATCH(BG$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(BG$1,$A:$A,0)),INDEX($F:$F,MATCH(BG$1,$A:$A,0)),INDEX($I:$I,MATCH(BG$1,$A:$A,0)),INDEX($L:$L,MATCH(BG$1,$A:$A,0)),INDEX($O:$O,MATCH(BG$1,$A:$A,0)),INDEX($R:$R,MATCH(BG$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="BI70" s="4" t="e">
+      <c r="BI70" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>#DIV/0!</v>
+        <v>7</v>
       </c>
       <c r="BJ70">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:62" x14ac:dyDescent="0.45">
@@ -18055,7 +18179,7 @@
       </c>
       <c r="AA72" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AC72" t="str" cm="1">
         <f t="array" ref="AC72">IFERROR(INDEX(CHOOSE(MATCH($X72,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -18087,9 +18211,8 @@
         <f t="array" ref="AJ72">IFERROR(INDEX(CHOOSE(MATCH($X72,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK72" t="str" cm="1">
-        <f t="array" ref="AK72">IFERROR(INDEX(CHOOSE(MATCH($X72,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK72">
+        <v>1</v>
       </c>
       <c r="AL72" t="str" cm="1">
         <f t="array" ref="AL72">IFERROR(INDEX(CHOOSE(MATCH($X72,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -18181,11 +18304,11 @@
       </c>
       <c r="BI72" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BJ72">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:62" x14ac:dyDescent="0.45">
@@ -18641,7 +18764,7 @@
       <c r="Z76" s="6"/>
       <c r="AA76" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AC76" t="str" cm="1">
         <f t="array" ref="AC76">IFERROR(INDEX(CHOOSE(MATCH($X76,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -18671,9 +18794,8 @@
         <f t="array" ref="AJ76">IFERROR(INDEX(CHOOSE(MATCH($X76,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK76" t="str" cm="1">
-        <f t="array" ref="AK76">IFERROR(INDEX(CHOOSE(MATCH($X76,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK76">
+        <v>2</v>
       </c>
       <c r="AL76" t="str" cm="1">
         <f t="array" ref="AL76">IFERROR(INDEX(CHOOSE(MATCH($X76,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -18765,11 +18887,11 @@
       </c>
       <c r="BI76" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BJ76">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:62" x14ac:dyDescent="0.45">
@@ -19660,7 +19782,7 @@
       <c r="Z83" s="6"/>
       <c r="AA83" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3</v>
+        <v>3.125</v>
       </c>
       <c r="AB83">
         <v>1</v>
@@ -19691,9 +19813,8 @@
         <f t="array" ref="AJ83">IFERROR(INDEX(CHOOSE(MATCH($X83,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK83" t="str" cm="1">
-        <f t="array" ref="AK83">IFERROR(INDEX(CHOOSE(MATCH($X83,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK83">
+        <v>4</v>
       </c>
       <c r="AL83" t="str" cm="1">
         <f t="array" ref="AL83">IFERROR(INDEX(CHOOSE(MATCH($X83,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -19785,11 +19906,11 @@
       </c>
       <c r="BI83" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>3</v>
+        <v>3.125</v>
       </c>
       <c r="BJ83">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:62" x14ac:dyDescent="0.45">
@@ -19948,10 +20069,12 @@
       <c r="X85" t="s">
         <v>54</v>
       </c>
-      <c r="Z85" s="6"/>
+      <c r="Z85" s="6">
+        <v>1</v>
+      </c>
       <c r="AA85" s="10">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>1</v>
+        <v>-0.66666666666666663</v>
       </c>
       <c r="AC85" t="str" cm="1">
         <f t="array" ref="AC85">IFERROR(INDEX(CHOOSE(MATCH($X85,INDEX($B:$R,MATCH(AC$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AC$1,$A:$A,0)),INDEX($F:$F,MATCH(AC$1,$A:$A,0)),INDEX($I:$I,MATCH(AC$1,$A:$A,0)),INDEX($L:$L,MATCH(AC$1,$A:$A,0)),INDEX($O:$O,MATCH(AC$1,$A:$A,0)),INDEX($R:$R,MATCH(AC$1,$A:$A,0))),1),"")</f>
@@ -19983,9 +20106,8 @@
         <f t="array" ref="AJ85">IFERROR(INDEX(CHOOSE(MATCH($X85,INDEX($B:$R,MATCH(AJ$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AJ$1,$A:$A,0)),INDEX($F:$F,MATCH(AJ$1,$A:$A,0)),INDEX($I:$I,MATCH(AJ$1,$A:$A,0)),INDEX($L:$L,MATCH(AJ$1,$A:$A,0)),INDEX($O:$O,MATCH(AJ$1,$A:$A,0)),INDEX($R:$R,MATCH(AJ$1,$A:$A,0))),1),"")</f>
         <v/>
       </c>
-      <c r="AK85" t="str" cm="1">
-        <f t="array" ref="AK85">IFERROR(INDEX(CHOOSE(MATCH($X85,INDEX($B:$R,MATCH(AK$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AK$1,$A:$A,0)),INDEX($F:$F,MATCH(AK$1,$A:$A,0)),INDEX($I:$I,MATCH(AK$1,$A:$A,0)),INDEX($L:$L,MATCH(AK$1,$A:$A,0)),INDEX($O:$O,MATCH(AK$1,$A:$A,0)),INDEX($R:$R,MATCH(AK$1,$A:$A,0))),1),"")</f>
-        <v/>
+      <c r="AK85">
+        <v>-4</v>
       </c>
       <c r="AL85" t="str" cm="1">
         <f t="array" ref="AL85">IFERROR(INDEX(CHOOSE(MATCH($X85,INDEX($B:$R,MATCH(AL$1,$A:$A,0),{1,4,7,10,13,16}),0),INDEX($C:$C,MATCH(AL$1,$A:$A,0)),INDEX($F:$F,MATCH(AL$1,$A:$A,0)),INDEX($I:$I,MATCH(AL$1,$A:$A,0)),INDEX($L:$L,MATCH(AL$1,$A:$A,0)),INDEX($O:$O,MATCH(AL$1,$A:$A,0)),INDEX($R:$R,MATCH(AL$1,$A:$A,0))),1),"")</f>
@@ -20077,11 +20199,11 @@
       </c>
       <c r="BI85" s="4">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>1</v>
+        <v>-0.66666666666666663</v>
       </c>
       <c r="BJ85">
         <f>COUNT(Table2[[#This Row],[11-Mar]:[Column33]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:62" x14ac:dyDescent="0.45">
@@ -21776,11 +21898,11 @@
       </c>
       <c r="B8" s="17">
         <f>SUM(Table2[[#This Row],[Wins ]]+Table3[[#This Row],[2Pot]]*0.5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -21788,7 +21910,7 @@
       </c>
       <c r="E8" s="20">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>2.875</v>
+        <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -21846,7 +21968,7 @@
       </c>
       <c r="C11" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -21854,7 +21976,7 @@
       </c>
       <c r="E11" s="19">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>0</v>
+        <v>-0.33333333333333331</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22022,7 +22144,7 @@
       </c>
       <c r="C19" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22030,7 +22152,7 @@
       </c>
       <c r="E19" s="19">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>-0.33333333333333331</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22110,7 +22232,7 @@
       </c>
       <c r="C23" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22118,7 +22240,7 @@
       </c>
       <c r="E23" s="20">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>3.3333333333333335</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22132,7 +22254,7 @@
       </c>
       <c r="C24" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22140,7 +22262,7 @@
       </c>
       <c r="E24" s="19">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22308,7 +22430,7 @@
       </c>
       <c r="C32" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22316,7 +22438,7 @@
       </c>
       <c r="E32" s="27">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>-0.66666666666666663</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22462,7 +22584,7 @@
       </c>
       <c r="C39" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22470,7 +22592,7 @@
       </c>
       <c r="E39" s="20">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>-2.75</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22501,11 +22623,11 @@
       </c>
       <c r="B41" s="17">
         <f>SUM(Table2[[#This Row],[Wins ]]+Table3[[#This Row],[2Pot]]*0.5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22513,7 +22635,7 @@
       </c>
       <c r="E41" s="20">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>1.6666666666666667</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22523,11 +22645,11 @@
       </c>
       <c r="B42" s="17">
         <f>SUM(Table2[[#This Row],[Wins ]]+Table3[[#This Row],[2Pot]]*0.5)</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="C42" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D42" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22535,7 +22657,7 @@
       </c>
       <c r="E42" s="19">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22703,7 +22825,7 @@
       </c>
       <c r="C50" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22711,7 +22833,7 @@
       </c>
       <c r="E50" s="27">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>2.5</v>
+        <v>2.3333333333333335</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -22813,7 +22935,7 @@
       </c>
       <c r="C55" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -22821,7 +22943,7 @@
       </c>
       <c r="E55" s="20">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23077,7 +23199,7 @@
       </c>
       <c r="C67" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D67" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -23085,7 +23207,7 @@
       </c>
       <c r="E67" s="32">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>2.125</v>
+        <v>2.1111111111111112</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23139,19 +23261,19 @@
       </c>
       <c r="B70" s="17">
         <f>SUM(Table2[[#This Row],[Wins ]]+Table3[[#This Row],[2Pot]]*0.5)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C70" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="E70" s="33">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>#DIV/0!</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23187,7 +23309,7 @@
       </c>
       <c r="C72" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -23195,7 +23317,7 @@
       </c>
       <c r="E72" s="32">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23275,7 +23397,7 @@
       </c>
       <c r="C76" s="18">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -23283,7 +23405,7 @@
       </c>
       <c r="E76" s="32">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23428,7 +23550,7 @@
       </c>
       <c r="C83" s="26">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -23436,7 +23558,7 @@
       </c>
       <c r="E83" s="11">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>3</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23468,11 +23590,11 @@
       </c>
       <c r="B85" s="41">
         <f>SUM(Table2[[#This Row],[Wins ]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" s="26">
         <f>SUM(Table2[[#This Row],[number of rounds]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D85" s="18">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
@@ -23480,7 +23602,7 @@
       </c>
       <c r="E85" s="11">
         <f>AVERAGE(Table2[[#This Row],[11-Mar]:[15-Jul]])</f>
-        <v>1</v>
+        <v>-0.66666666666666663</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -23599,7 +23721,7 @@
       <c r="B91" s="31"/>
       <c r="C91" s="26">
         <f>SUM(C2:C90)</f>
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D91" s="18"/>
     </row>
@@ -24328,7 +24450,7 @@
       </c>
       <c r="B70" s="23">
         <f>SUM(Table2[[#This Row],[2 Pot]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="18" x14ac:dyDescent="0.55000000000000004">
@@ -24774,16 +24896,16 @@
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5B97C3B-856C-4B5A-B09B-A22E704BFD5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="d4f655e1-431c-4afd-8d59-6cad9d770740"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="28901c16-d4d5-4d31-a6ad-2d0fba0de9e2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="28901c16-d4d5-4d31-a6ad-2d0fba0de9e2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d4f655e1-431c-4afd-8d59-6cad9d770740"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>